--- a/data/trans_orig/P19C09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Provincia-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2007 (tasa de respuesta: 99,82%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1607</t>
+          <t>1688</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9776</t>
+          <t>10549</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2345</t>
+          <t>2234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>13572</t>
+          <t>14329</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,74%</t>
+          <t>7,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6203</t>
+          <t>6219</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>19346</t>
+          <t>20824</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -822,7 +822,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>5,3%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>181717</t>
+          <t>180944</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189886</t>
+          <t>189805</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,89%</t>
+          <t>94,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>187650</t>
+          <t>186893</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198877</t>
+          <t>198988</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>93,26%</t>
+          <t>92,88%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>373370</t>
+          <t>371892</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386513</t>
+          <t>386497</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,7%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>6992</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23834</t>
+          <t>23442</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,83%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8628</t>
+          <t>8902</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24043</t>
+          <t>24459</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,54%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19693</t>
+          <t>19679</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41320</t>
+          <t>41960</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,94%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384882</t>
+          <t>385274</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401724</t>
+          <t>401487</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,17%</t>
+          <t>94,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,29%</t>
+          <t>98,23%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>417158</t>
+          <t>416742</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432573</t>
+          <t>432299</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>94,46%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,04%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>808597</t>
+          <t>807957</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>830224</t>
+          <t>830238</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,14%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1821</t>
+          <t>1754</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10016</t>
+          <t>10273</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5958</t>
+          <t>5920</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>18958</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,73%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>9466</t>
+          <t>8713</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24376</t>
+          <t>24797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,8%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>4,72%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226521</t>
+          <t>226264</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>234716</t>
+          <t>234783</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,77%</t>
+          <t>95,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269848</t>
+          <t>269379</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>282848</t>
+          <t>282886</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,44%</t>
+          <t>93,27%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,94%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>500967</t>
+          <t>500546</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>515877</t>
+          <t>516630</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,28%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,2%</t>
+          <t>98,34%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4495</t>
+          <t>4363</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18744</t>
+          <t>18357</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4882</t>
+          <t>4951</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>17750</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11522</t>
+          <t>11648</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29098</t>
+          <t>28665</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,05%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>248787</t>
+          <t>249174</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263036</t>
+          <t>263168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>93,14%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>282936</t>
+          <t>281784</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294652</t>
+          <t>294583</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,35%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>537967</t>
+          <t>538400</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>555543</t>
+          <t>555417</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,87%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,97%</t>
+          <t>97,95%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2539</t>
+          <t>2524</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12534</t>
+          <t>12943</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1877</t>
+          <t>1910</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11464</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6026</t>
+          <t>5509</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19052</t>
+          <t>18997</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,52%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157744</t>
+          <t>157335</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167739</t>
+          <t>167754</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,4%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,51%</t>
+          <t>98,52%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>162442</t>
+          <t>163042</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>172029</t>
+          <t>171996</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,41%</t>
+          <t>93,75%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325132</t>
+          <t>325187</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338158</t>
+          <t>338675</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,4%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>1033</t>
+          <t>1035</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9689</t>
+          <t>9563</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,12%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>2127</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>11146</t>
+          <t>12761</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4293</t>
+          <t>4311</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>17243</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2537,7 +2537,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,2%</t>
+          <t>4,38%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179581</t>
+          <t>179707</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>188237</t>
+          <t>188235</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,88%</t>
+          <t>94,95%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>193342</t>
+          <t>191727</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202581</t>
+          <t>202361</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>94,55%</t>
+          <t>93,76%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>377233</t>
+          <t>376515</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>389465</t>
+          <t>389447</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,7 +2645,7 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,8%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5845</t>
+          <t>5577</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19605</t>
+          <t>19600</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,7 +2805,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>14907</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>34536</t>
+          <t>35473</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24193</t>
+          <t>24181</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47937</t>
+          <t>47454</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,78%</t>
+          <t>4,73%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>444720</t>
+          <t>444725</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>458480</t>
+          <t>458748</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2923,7 +2923,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>504832</t>
+          <t>503895</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>524461</t>
+          <t>523895</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,6%</t>
+          <t>93,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,13%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>955755</t>
+          <t>956238</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>979499</t>
+          <t>979511</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,27%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6400</t>
+          <t>5892</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19158</t>
+          <t>19405</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4572</t>
+          <t>4540</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>17986</t>
+          <t>19078</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,77%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>12922</t>
+          <t>13270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>32037</t>
+          <t>33452</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>503183</t>
+          <t>502936</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>515941</t>
+          <t>516449</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,33%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,87%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>570744</t>
+          <t>569652</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>584158</t>
+          <t>584190</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,94%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,23%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1079034</t>
+          <t>1077619</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1098149</t>
+          <t>1097801</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,12%</t>
+          <t>96,99%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,84%</t>
+          <t>98,81%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49747</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80395</t>
+          <t>80461</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>69534</t>
+          <t>68707</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106829</t>
+          <t>105070</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>126092</t>
+          <t>127168</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>178096</t>
+          <t>175380</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,38%</t>
         </is>
       </c>
     </row>
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2370096</t>
+          <t>2370030</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2400744</t>
+          <t>2400680</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2630426</t>
+          <t>2632185</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2667721</t>
+          <t>2668548</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3639,12 +3639,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,1%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,49%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5009649</t>
+          <t>5012365</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5061653</t>
+          <t>5060577</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3674,12 +3674,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,55%</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3860,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2012 (tasa de respuesta: 97,46%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>933</t>
+          <t>939</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>12481</t>
+          <t>11396</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,38%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,0%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>11494</t>
+          <t>10847</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>28624</t>
+          <t>30189</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,48%</t>
+          <t>12,11%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14609</t>
+          <t>14315</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>35491</t>
+          <t>36219</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,11%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>237265</t>
+          <t>238350</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248813</t>
+          <t>248807</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,0%</t>
+          <t>95,44%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,62%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>220615</t>
+          <t>219050</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>237745</t>
+          <t>238392</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>87,89%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>463494</t>
+          <t>462766</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484376</t>
+          <t>484670</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,89%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,07%</t>
+          <t>97,13%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1880</t>
+          <t>1939</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>10895</t>
+          <t>11174</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4151</t>
+          <t>4075</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>18904</t>
+          <t>17146</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7232</t>
+          <t>7899</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>23704</t>
+          <t>24413</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,98%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,03%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>384055</t>
+          <t>383776</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393070</t>
+          <t>393011</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,52%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>393094</t>
+          <t>394852</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>407847</t>
+          <t>407923</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,41%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>98,99%</t>
+          <t>99,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>783244</t>
+          <t>782535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799716</t>
+          <t>799049</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,1%</t>
+          <t>99,02%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1009</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10963</t>
+          <t>9201</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,35%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5086</t>
+          <t>4282</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>17185</t>
+          <t>16941</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,23%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8031</t>
+          <t>8087</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22925</t>
+          <t>22964</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281766</t>
+          <t>283528</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291715</t>
+          <t>291720</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,65%</t>
+          <t>99,66%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311567</t>
+          <t>311811</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>323666</t>
+          <t>324470</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,77%</t>
+          <t>94,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>98,45%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598556</t>
+          <t>598517</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613450</t>
+          <t>613394</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,31%</t>
+          <t>96,3%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,7%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4935</t>
+          <t>5049</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19043</t>
+          <t>19489</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7620</t>
+          <t>7072</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>23176</t>
+          <t>21966</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14693</t>
+          <t>14875</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>35877</t>
+          <t>34653</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,35%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>288028</t>
+          <t>287582</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302136</t>
+          <t>302022</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,8%</t>
+          <t>93,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,36%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>317518</t>
+          <t>318728</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333074</t>
+          <t>333622</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,2%</t>
+          <t>93,55%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,92%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>611888</t>
+          <t>613112</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>633072</t>
+          <t>632890</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,7%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>989</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8298</t>
+          <t>8337</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>982</t>
+          <t>979</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10918</t>
+          <t>11502</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5482,7 +5482,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2999</t>
+          <t>2714</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>14757</t>
+          <t>13831</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,84%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,27%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>149156</t>
+          <t>149117</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156442</t>
+          <t>156465</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,37%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155722</t>
+          <t>155138</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165658</t>
+          <t>165661</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,7 +5590,7 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,1%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>309337</t>
+          <t>310263</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>321095</t>
+          <t>321380</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,45%</t>
+          <t>95,73%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,07%</t>
+          <t>99,16%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>975</t>
+          <t>970</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9837</t>
+          <t>8949</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,59%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>3903</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>17033</t>
+          <t>16657</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,29%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6894</t>
+          <t>6805</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21540</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,14%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>239177</t>
+          <t>240065</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248039</t>
+          <t>248044</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,7 +5898,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,41%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>247797</t>
+          <t>248173</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260906</t>
+          <t>260927</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,57%</t>
+          <t>93,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492304</t>
+          <t>492562</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>506950</t>
+          <t>507039</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,81%</t>
+          <t>95,86%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,68%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7746</t>
+          <t>7699</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23143</t>
+          <t>23964</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7668</t>
+          <t>6945</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>22896</t>
+          <t>21965</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,66%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>17769</t>
+          <t>18130</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>38629</t>
+          <t>40435</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,37%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>551010</t>
+          <t>550189</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>566407</t>
+          <t>566454</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,97%</t>
+          <t>95,83%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,65%</t>
+          <t>98,66%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>602124</t>
+          <t>603055</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>617352</t>
+          <t>618075</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,49%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1160544</t>
+          <t>1158738</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1181404</t>
+          <t>1181043</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,78%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,52%</t>
+          <t>98,49%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1991</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>13410</t>
+          <t>12076</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3636</t>
+          <t>3766</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>15605</t>
+          <t>16550</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>0,55%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>7397</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>22811</t>
+          <t>23777</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6541,12 +6541,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>598193</t>
+          <t>599527</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>609612</t>
+          <t>610561</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>97,81%</t>
+          <t>98,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,67%</t>
+          <t>99,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>667406</t>
+          <t>666461</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>679375</t>
+          <t>679245</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,72%</t>
+          <t>97,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,47%</t>
+          <t>99,45%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1271802</t>
+          <t>1270836</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1287329</t>
+          <t>1287216</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,12 +6654,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,43%</t>
         </is>
       </c>
     </row>
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>35840</t>
+          <t>34584</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>65963</t>
+          <t>63186</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>68765</t>
+          <t>66714</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>106697</t>
+          <t>105433</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,24%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>114248</t>
+          <t>111290</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>163248</t>
+          <t>159439</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6884,12 +6884,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2770756</t>
+          <t>2773533</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2800879</t>
+          <t>2802135</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,74%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2963487</t>
+          <t>2964751</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3001419</t>
+          <t>3003470</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,52%</t>
+          <t>96,57%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,76%</t>
+          <t>97,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5743655</t>
+          <t>5747464</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5792655</t>
+          <t>5795613</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,24%</t>
+          <t>97,3%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,12%</t>
         </is>
       </c>
     </row>
@@ -7183,7 +7183,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016</t>
+          <t>Población según si el motivo por su última visita al dentista fue por otros motivos en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5849</t>
+          <t>6230</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19117</t>
+          <t>19968</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5604</t>
+          <t>5773</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20759</t>
+          <t>20074</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14184</t>
+          <t>14464</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>33030</t>
+          <t>32787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,67%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>226101</t>
+          <t>225250</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>239369</t>
+          <t>238988</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,61%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>225575</t>
+          <t>226260</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>240730</t>
+          <t>240561</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,57%</t>
+          <t>91,85%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,73%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458521</t>
+          <t>458764</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>477367</t>
+          <t>477087</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,28%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,11%</t>
+          <t>97,06%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4864</t>
+          <t>4493</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17806</t>
+          <t>17209</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,9%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1981</t>
+          <t>2010</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12405</t>
+          <t>11877</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8392</t>
+          <t>8824</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24926</t>
+          <t>24700</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345359</t>
+          <t>345956</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358301</t>
+          <t>358672</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,1%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>380922</t>
+          <t>381450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>391346</t>
+          <t>391317</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731566</t>
+          <t>731792</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>748100</t>
+          <t>747668</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,83%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>787</t>
+          <t>783</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9142</t>
+          <t>8781</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>927</t>
+          <t>932</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>12450</t>
+          <t>11005</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2584</t>
+          <t>2778</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14549</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281365</t>
+          <t>281726</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289720</t>
+          <t>289724</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,85%</t>
+          <t>96,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>295314</t>
+          <t>296759</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306837</t>
+          <t>306832</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>583721</t>
+          <t>583170</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>595686</t>
+          <t>595492</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,54%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14860</t>
+          <t>14862</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33867</t>
+          <t>33564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8427,7 +8427,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,26%</t>
+          <t>10,17%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>10964</t>
+          <t>11150</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27106</t>
+          <t>28049</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>8,04%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>30017</t>
+          <t>28892</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54396</t>
+          <t>54378</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,7 +8492,7 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296180</t>
+          <t>296483</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315187</t>
+          <t>315185</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,7 +8535,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>321755</t>
+          <t>320812</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>337897</t>
+          <t>337711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,8%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>624512</t>
+          <t>624530</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>648891</t>
+          <t>650016</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8610,7 +8610,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,74%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1730</t>
+          <t>1907</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10315</t>
+          <t>10663</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2918</t>
+          <t>2815</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>12853</t>
+          <t>13109</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,83%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6442</t>
+          <t>6450</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19219</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,01%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108907</t>
+          <t>108559</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117492</t>
+          <t>117315</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,35%</t>
+          <t>91,06%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,55%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132647</t>
+          <t>132391</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142582</t>
+          <t>142685</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>91,17%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>245503</t>
+          <t>246171</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258280</t>
+          <t>258272</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,57%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7233</t>
+          <t>6013</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1886</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>12235</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9143,12 +9143,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>2985</t>
+          <t>3356</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>14404</t>
+          <t>15838</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,29%</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>226382</t>
+          <t>227602</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,9%</t>
+          <t>97,43%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>235082</t>
+          <t>234902</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245216</t>
+          <t>245251</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,12 +9256,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,05%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,24%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>466349</t>
+          <t>464915</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>477768</t>
+          <t>477397</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>97,0%</t>
+          <t>96,71%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,3%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4359</t>
+          <t>4500</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19559</t>
+          <t>19365</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,12 +9451,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>8039</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>24185</t>
+          <t>23174</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>15798</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>35659</t>
+          <t>36689</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9526,7 +9526,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,95%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>422748</t>
+          <t>422942</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>437948</t>
+          <t>437807</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9564,12 +9564,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,62%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>462866</t>
+          <t>463877</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>479012</t>
+          <t>479191</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>95,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>893699</t>
+          <t>892669</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>913592</t>
+          <t>913560</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,7 +9634,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>6925</t>
+          <t>7197</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21959</t>
+          <t>21483</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5308</t>
+          <t>5399</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>20321</t>
+          <t>19361</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15823</t>
+          <t>15238</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>36869</t>
+          <t>35765</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,69%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>618293</t>
+          <t>618769</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>633327</t>
+          <t>633055</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>671020</t>
+          <t>671980</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>686033</t>
+          <t>685942</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,22%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1294724</t>
+          <t>1295828</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1315770</t>
+          <t>1316355</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,23%</t>
+          <t>97,31%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61151</t>
+          <t>61511</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96900</t>
+          <t>96961</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,7 +10137,7 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59388</t>
+          <t>59852</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>95811</t>
+          <t>96283</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,07%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,36%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>128980</t>
+          <t>130042</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>177268</t>
+          <t>179356</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2567433</t>
+          <t>2567372</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2603182</t>
+          <t>2602822</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10255,7 +10255,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,69%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2771504</t>
+          <t>2771032</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2807927</t>
+          <t>2807463</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,66%</t>
+          <t>96,64%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,93%</t>
+          <t>97,91%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5354380</t>
+          <t>5352292</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5402668</t>
+          <t>5401606</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,76%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,67%</t>
+          <t>97,65%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P19C09-Provincia-trans_orig.xlsx
+++ b/data/trans_orig/P19C09-Provincia-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1688</t>
+          <t>1749</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>9946</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2234</t>
+          <t>2434</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>14329</t>
+          <t>13277</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>7,12%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6219</t>
+          <t>5846</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>20824</t>
+          <t>19867</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,06%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>180944</t>
+          <t>181547</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>189805</t>
+          <t>189744</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>94,49%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,12%</t>
+          <t>99,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>186893</t>
+          <t>187945</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>198988</t>
+          <t>198788</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>92,88%</t>
+          <t>93,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,79%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>371892</t>
+          <t>372849</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>386497</t>
+          <t>386870</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>94,7%</t>
+          <t>94,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,51%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7060</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23442</t>
+          <t>22983</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8902</t>
+          <t>8782</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>24459</t>
+          <t>23864</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19679</t>
+          <t>18898</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>41960</t>
+          <t>40003</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>4,94%</t>
+          <t>4,71%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>385274</t>
+          <t>385733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>401487</t>
+          <t>401656</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>94,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>416742</t>
+          <t>417337</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>432299</t>
+          <t>432419</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>94,46%</t>
+          <t>94,59%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>98,01%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>807957</t>
+          <t>809914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>830238</t>
+          <t>831019</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>97,68%</t>
+          <t>97,78%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>1785</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>10273</t>
+          <t>10243</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,75%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>4,34%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>5920</t>
+          <t>6082</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>19427</t>
+          <t>19707</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8713</t>
+          <t>9517</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>24797</t>
+          <t>24584</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,68%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>226264</t>
+          <t>226294</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>234783</t>
+          <t>234752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>95,66%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,26%</t>
+          <t>99,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>269379</t>
+          <t>269099</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>282886</t>
+          <t>282724</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>93,27%</t>
+          <t>93,18%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>500546</t>
+          <t>500759</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>516630</t>
+          <t>515826</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>95,28%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,34%</t>
+          <t>98,19%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>4363</t>
+          <t>4280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>18357</t>
+          <t>17794</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,86%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4951</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>17750</t>
+          <t>16863</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,65%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>5,93%</t>
+          <t>5,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11648</t>
+          <t>11381</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28665</t>
+          <t>29058</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>5,12%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>249174</t>
+          <t>249737</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>263168</t>
+          <t>263251</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,14%</t>
+          <t>93,35%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,37%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>281784</t>
+          <t>282671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>294583</t>
+          <t>294736</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>94,07%</t>
+          <t>94,37%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,35%</t>
+          <t>98,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>538400</t>
+          <t>538007</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>555417</t>
+          <t>555684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>94,88%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,99%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2526</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>12943</t>
+          <t>13534</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,6%</t>
+          <t>7,95%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>1910</t>
+          <t>1817</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>10864</t>
+          <t>10708</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5509</t>
+          <t>5352</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18997</t>
+          <t>19036</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>5,53%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>157335</t>
+          <t>156744</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>167754</t>
+          <t>167752</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,7 +2232,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>92,4%</t>
+          <t>92,05%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>163042</t>
+          <t>163198</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>171996</t>
+          <t>172089</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,75%</t>
+          <t>93,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>98,96%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>325187</t>
+          <t>325148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>338675</t>
+          <t>338832</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,45%</t>
         </is>
       </c>
     </row>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>9563</t>
+          <t>9382</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2467,7 +2467,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2127</t>
+          <t>1970</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12761</t>
+          <t>11698</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>4311</t>
+          <t>4350</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>17243</t>
+          <t>17836</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,38%</t>
+          <t>4,53%</t>
         </is>
       </c>
     </row>
@@ -2560,7 +2560,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>179707</t>
+          <t>179888</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -2575,7 +2575,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>191727</t>
+          <t>192790</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>202361</t>
+          <t>202518</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,96%</t>
+          <t>99,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>376515</t>
+          <t>375922</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>389447</t>
+          <t>389408</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,62%</t>
+          <t>95,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5486</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19600</t>
+          <t>19309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>15473</t>
+          <t>15275</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>35473</t>
+          <t>34978</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>6,58%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>24181</t>
+          <t>24230</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>47454</t>
+          <t>47557</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2880,7 +2880,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>4,73%</t>
+          <t>4,74%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>444725</t>
+          <t>445016</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>458748</t>
+          <t>458839</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,78%</t>
+          <t>95,84%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,8%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>503895</t>
+          <t>504390</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>523895</t>
+          <t>524093</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>93,42%</t>
+          <t>93,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,17%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>956238</t>
+          <t>956135</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>979511</t>
+          <t>979462</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,7 +2988,7 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>95,27%</t>
+          <t>95,26%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>5892</t>
+          <t>6113</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>19405</t>
+          <t>18911</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>4540</t>
+          <t>5206</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19078</t>
+          <t>18731</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,77%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13270</t>
+          <t>13661</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>33452</t>
+          <t>31804</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>3,01%</t>
+          <t>2,86%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>502936</t>
+          <t>503430</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>516449</t>
+          <t>516228</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,29%</t>
+          <t>96,38%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,87%</t>
+          <t>98,83%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>569652</t>
+          <t>569999</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>584190</t>
+          <t>583524</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,23%</t>
+          <t>99,12%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1077619</t>
+          <t>1079267</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1097801</t>
+          <t>1097410</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>96,99%</t>
+          <t>97,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,81%</t>
+          <t>98,77%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>49811</t>
+          <t>49727</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>80461</t>
+          <t>81908</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,28%</t>
+          <t>3,34%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>68707</t>
+          <t>69568</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105070</t>
+          <t>105202</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3526,7 +3526,7 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>127168</t>
+          <t>126470</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>175380</t>
+          <t>175335</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3561,7 +3561,7 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
@@ -3589,12 +3589,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2370030</t>
+          <t>2368583</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2400680</t>
+          <t>2400764</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,72%</t>
+          <t>96,66%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
@@ -3624,12 +3624,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2632185</t>
+          <t>2632053</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2668548</t>
+          <t>2667687</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3644,7 +3644,7 @@
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,49%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3659,12 +3659,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5012365</t>
+          <t>5012410</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5060577</t>
+          <t>5061275</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3679,7 +3679,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,55%</t>
+          <t>97,56%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>1164</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11396</t>
+          <t>13820</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>5,53%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>10847</t>
+          <t>11073</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>30189</t>
+          <t>29718</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>12,11%</t>
+          <t>11,92%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14315</t>
+          <t>14287</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>36219</t>
+          <t>36888</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,39%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>238350</t>
+          <t>235926</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>248807</t>
+          <t>248582</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>95,44%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,62%</t>
+          <t>99,53%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>219050</t>
+          <t>219521</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>238392</t>
+          <t>238166</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>88,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>95,65%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>462766</t>
+          <t>462097</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>484670</t>
+          <t>484698</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>92,74%</t>
+          <t>92,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,13%</t>
+          <t>97,14%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>1939</t>
+          <t>1946</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11174</t>
+          <t>10183</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4418,7 +4418,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4075</t>
+          <t>4209</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>18283</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7899</t>
+          <t>8091</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24413</t>
+          <t>25034</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,1%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>383776</t>
+          <t>384767</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>393011</t>
+          <t>393004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4526,7 +4526,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>97,17%</t>
+          <t>97,42%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>394852</t>
+          <t>393715</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>407923</t>
+          <t>407789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>95,84%</t>
+          <t>95,56%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,01%</t>
+          <t>98,98%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>782535</t>
+          <t>781914</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>799049</t>
+          <t>798857</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,97%</t>
+          <t>96,9%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,02%</t>
+          <t>99,0%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1009</t>
+          <t>1004</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9201</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4761,7 +4761,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>4282</t>
+          <t>4270</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>16941</t>
+          <t>17052</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4796,7 +4796,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>5,15%</t>
+          <t>5,19%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>8087</t>
+          <t>8121</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>22964</t>
+          <t>22672</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,65%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>283528</t>
+          <t>282632</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>291720</t>
+          <t>291725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4869,7 +4869,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,55%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>311811</t>
+          <t>311700</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>324470</t>
+          <t>324482</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4904,7 +4904,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>94,85%</t>
+          <t>94,81%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>598517</t>
+          <t>598809</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>613394</t>
+          <t>613360</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>96,3%</t>
+          <t>96,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,69%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5049</t>
+          <t>4832</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>19489</t>
+          <t>18973</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,57%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>7072</t>
+          <t>7309</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21966</t>
+          <t>22895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>14875</t>
+          <t>15035</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>34653</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,6%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>287582</t>
+          <t>288098</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>302022</t>
+          <t>302239</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>93,65%</t>
+          <t>93,82%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,36%</t>
+          <t>98,43%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>318728</t>
+          <t>317799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>333622</t>
+          <t>333385</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>93,55%</t>
+          <t>93,28%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>97,92%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>613112</t>
+          <t>611498</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>632890</t>
+          <t>632730</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>94,65%</t>
+          <t>94,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>97,7%</t>
+          <t>97,68%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>989</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>8337</t>
+          <t>8309</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,28%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>979</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>11502</t>
+          <t>10929</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>0,59%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>2714</t>
+          <t>2087</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>13831</t>
+          <t>14047</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,33%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>149117</t>
+          <t>149145</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>156465</t>
+          <t>156441</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>94,71%</t>
+          <t>94,72%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>99,37%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>155138</t>
+          <t>155711</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>165661</t>
+          <t>165678</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>93,1%</t>
+          <t>93,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>99,41%</t>
+          <t>99,42%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>310263</t>
+          <t>310047</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>321380</t>
+          <t>322007</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>95,73%</t>
+          <t>95,67%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>99,16%</t>
+          <t>99,36%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>970</t>
+          <t>985</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8949</t>
+          <t>9667</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>0,39%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5805,12 +5805,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3903</t>
+          <t>4077</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>16657</t>
+          <t>17901</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5820,12 +5820,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>6805</t>
+          <t>6861</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>21282</t>
+          <t>22471</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,34%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>4,14%</t>
+          <t>4,37%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>240065</t>
+          <t>239347</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>248044</t>
+          <t>248029</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>96,41%</t>
+          <t>96,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>99,61%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5918,12 +5918,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>248173</t>
+          <t>246929</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>260927</t>
+          <t>260753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5933,12 +5933,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>93,71%</t>
+          <t>93,24%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,46%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>492562</t>
+          <t>491373</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>507039</t>
+          <t>506983</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>95,86%</t>
+          <t>95,63%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>98,68%</t>
+          <t>98,66%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7699</t>
+          <t>7055</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>23964</t>
+          <t>22944</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,34%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>4,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>6945</t>
+          <t>7687</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>21965</t>
+          <t>23157</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>18130</t>
+          <t>18469</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>40435</t>
+          <t>39525</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,3%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>550189</t>
+          <t>551209</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>566454</t>
+          <t>567098</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>95,83%</t>
+          <t>96,0%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,66%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>603055</t>
+          <t>601863</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>618075</t>
+          <t>617333</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>96,49%</t>
+          <t>96,29%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,89%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1158738</t>
+          <t>1159648</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1181043</t>
+          <t>1180704</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,46%</t>
         </is>
       </c>
     </row>
@@ -6456,12 +6456,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1993</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>12076</t>
+          <t>13037</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6471,12 +6471,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6491,12 +6491,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3766</t>
+          <t>4136</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>16550</t>
+          <t>16658</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6506,12 +6506,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,42%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6526,12 +6526,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>7397</t>
+          <t>7329</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>23777</t>
+          <t>24961</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>
@@ -6569,12 +6569,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>599527</t>
+          <t>598566</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>610561</t>
+          <t>609610</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6584,12 +6584,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>98,03%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>99,83%</t>
+          <t>99,67%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6604,12 +6604,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>666461</t>
+          <t>666353</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>679245</t>
+          <t>678875</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6619,12 +6619,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,58%</t>
+          <t>97,56%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6639,12 +6639,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1270836</t>
+          <t>1269652</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1287216</t>
+          <t>1287284</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6654,7 +6654,7 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>98,16%</t>
+          <t>98,07%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
@@ -6799,12 +6799,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>34584</t>
+          <t>36997</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>63186</t>
+          <t>66974</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6814,12 +6814,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>2,23%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6834,12 +6834,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>66714</t>
+          <t>69078</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>105433</t>
+          <t>106971</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6849,12 +6849,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6869,12 +6869,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>111290</t>
+          <t>111187</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>159439</t>
+          <t>160618</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6889,7 +6889,7 @@
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,72%</t>
         </is>
       </c>
     </row>
@@ -6912,12 +6912,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2773533</t>
+          <t>2769745</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2802135</t>
+          <t>2799722</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6927,12 +6927,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>97,77%</t>
+          <t>97,64%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -6947,12 +6947,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2964751</t>
+          <t>2963213</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>3003470</t>
+          <t>3001106</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -6962,12 +6962,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,52%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,75%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -6982,12 +6982,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5747464</t>
+          <t>5746285</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5795613</t>
+          <t>5795716</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -6997,7 +6997,7 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>97,3%</t>
+          <t>97,28%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
@@ -7378,12 +7378,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6230</t>
+          <t>5680</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>19968</t>
+          <t>19567</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7393,12 +7393,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,14%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7413,12 +7413,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5773</t>
+          <t>5901</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>20074</t>
+          <t>22599</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7428,12 +7428,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7448,12 +7448,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>14464</t>
+          <t>14197</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>32787</t>
+          <t>32571</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7463,12 +7463,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -7491,12 +7491,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>225250</t>
+          <t>225651</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>238988</t>
+          <t>239538</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7506,12 +7506,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>91,86%</t>
+          <t>92,02%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7526,12 +7526,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>226260</t>
+          <t>223735</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>240561</t>
+          <t>240433</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7541,12 +7541,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>91,85%</t>
+          <t>90,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7561,12 +7561,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>458764</t>
+          <t>458980</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>477087</t>
+          <t>477354</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7576,12 +7576,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,11%</t>
         </is>
       </c>
     </row>
@@ -7721,12 +7721,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>4493</t>
+          <t>4794</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>17209</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7736,12 +7736,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>4,74%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7756,12 +7756,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2010</t>
+          <t>2060</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11877</t>
+          <t>11717</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7771,12 +7771,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7791,12 +7791,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>8824</t>
+          <t>8617</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>24700</t>
+          <t>25869</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7806,12 +7806,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,42%</t>
         </is>
       </c>
     </row>
@@ -7834,12 +7834,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>345956</t>
+          <t>345642</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>358672</t>
+          <t>358371</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7849,12 +7849,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>95,26%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>98,76%</t>
+          <t>98,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7869,12 +7869,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>381450</t>
+          <t>381610</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>391317</t>
+          <t>391267</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7884,12 +7884,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,49%</t>
+          <t>99,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7904,12 +7904,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>731792</t>
+          <t>730623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>747668</t>
+          <t>747875</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7919,12 +7919,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>96,73%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>98,83%</t>
+          <t>98,86%</t>
         </is>
       </c>
     </row>
@@ -8064,12 +8064,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>782</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8781</t>
+          <t>8147</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8084,7 +8084,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8099,12 +8099,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>925</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>11005</t>
+          <t>11994</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -8119,7 +8119,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,9%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -8134,12 +8134,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2778</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>15100</t>
+          <t>15512</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -8149,12 +8149,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,59%</t>
         </is>
       </c>
     </row>
@@ -8177,12 +8177,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>281726</t>
+          <t>282360</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>289724</t>
+          <t>289725</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8192,7 +8192,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>97,2%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -8212,12 +8212,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>296759</t>
+          <t>295770</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>306832</t>
+          <t>306839</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8227,7 +8227,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,42%</t>
+          <t>96,1%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -8247,12 +8247,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>583170</t>
+          <t>582758</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>595492</t>
+          <t>595447</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8262,12 +8262,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,48%</t>
+          <t>97,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,54%</t>
+          <t>99,53%</t>
         </is>
       </c>
     </row>
@@ -8407,12 +8407,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14862</t>
+          <t>14910</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>33564</t>
+          <t>33204</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8422,12 +8422,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,17%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8442,12 +8442,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11150</t>
+          <t>10797</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>28049</t>
+          <t>27763</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8457,12 +8457,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,04%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8477,12 +8477,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>28892</t>
+          <t>30293</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>54378</t>
+          <t>55838</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8492,12 +8492,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,46%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,22%</t>
         </is>
       </c>
     </row>
@@ -8520,12 +8520,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>296483</t>
+          <t>296843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>315185</t>
+          <t>315137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8535,12 +8535,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,83%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,5%</t>
+          <t>95,48%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8555,12 +8555,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>320812</t>
+          <t>321098</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>337711</t>
+          <t>338064</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>91,96%</t>
+          <t>92,04%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>96,8%</t>
+          <t>96,91%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8590,12 +8590,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>624530</t>
+          <t>623070</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>650016</t>
+          <t>648615</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8605,12 +8605,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>91,99%</t>
+          <t>91,78%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,74%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -8750,12 +8750,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1907</t>
+          <t>1786</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10343</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8765,12 +8765,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,5%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8785,12 +8785,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2815</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>13109</t>
+          <t>12817</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8800,12 +8800,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>8,81%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8820,12 +8820,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6450</t>
+          <t>6505</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>18551</t>
+          <t>19793</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8835,12 +8835,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,48%</t>
         </is>
       </c>
     </row>
@@ -8863,12 +8863,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>108559</t>
+          <t>108879</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>117315</t>
+          <t>117436</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8878,12 +8878,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>91,06%</t>
+          <t>91,32%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>98,4%</t>
+          <t>98,5%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8898,12 +8898,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>132391</t>
+          <t>132683</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>142685</t>
+          <t>142554</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8913,12 +8913,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>91,19%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8933,12 +8933,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>246171</t>
+          <t>244929</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>258272</t>
+          <t>258217</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8948,12 +8948,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>92,99%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>97,56%</t>
+          <t>97,54%</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6013</t>
+          <t>6902</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9113,7 +9113,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9128,12 +9128,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1886</t>
+          <t>1891</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12235</t>
+          <t>12593</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9148,7 +9148,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9163,12 +9163,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>3356</t>
+          <t>2944</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>15838</t>
+          <t>14673</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9178,12 +9178,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>3,29%</t>
+          <t>3,05%</t>
         </is>
       </c>
     </row>
@@ -9206,7 +9206,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>227602</t>
+          <t>226713</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -9221,7 +9221,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -9241,12 +9241,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>234902</t>
+          <t>234544</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>245251</t>
+          <t>245246</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9256,7 +9256,7 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>95,05%</t>
+          <t>94,9%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
@@ -9276,12 +9276,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>464915</t>
+          <t>466080</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>477397</t>
+          <t>477809</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9291,12 +9291,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>96,71%</t>
+          <t>96,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,39%</t>
         </is>
       </c>
     </row>
@@ -9436,12 +9436,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>4500</t>
+          <t>4564</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>19365</t>
+          <t>19386</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9451,7 +9451,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
@@ -9471,12 +9471,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>7924</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>23174</t>
+          <t>24211</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -9486,12 +9486,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -9506,12 +9506,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>15798</t>
+          <t>16247</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>36689</t>
+          <t>36581</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9521,12 +9521,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,94%</t>
         </is>
       </c>
     </row>
@@ -9549,12 +9549,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>422942</t>
+          <t>422921</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>437807</t>
+          <t>437743</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -9569,7 +9569,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>98,98%</t>
+          <t>98,97%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -9584,12 +9584,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>463877</t>
+          <t>462840</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>479191</t>
+          <t>479127</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -9599,12 +9599,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>95,24%</t>
+          <t>95,03%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -9619,12 +9619,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>892669</t>
+          <t>892777</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>913560</t>
+          <t>913111</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -9634,12 +9634,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>96,05%</t>
+          <t>96,06%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>98,3%</t>
+          <t>98,25%</t>
         </is>
       </c>
     </row>
@@ -9779,12 +9779,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>7197</t>
+          <t>7050</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>21483</t>
+          <t>21282</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9794,12 +9794,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9814,12 +9814,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>5399</t>
+          <t>4545</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>19361</t>
+          <t>19285</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9829,12 +9829,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,66%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9849,12 +9849,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>15238</t>
+          <t>15000</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>35765</t>
+          <t>37071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9864,12 +9864,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,78%</t>
         </is>
       </c>
     </row>
@@ -9892,12 +9892,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>618769</t>
+          <t>618970</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>633055</t>
+          <t>633202</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9907,12 +9907,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,68%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>98,88%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9927,12 +9927,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>671980</t>
+          <t>672056</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>685942</t>
+          <t>686796</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9942,12 +9942,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>97,2%</t>
+          <t>97,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9962,12 +9962,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1295828</t>
+          <t>1294522</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1316355</t>
+          <t>1316593</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9977,12 +9977,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>97,31%</t>
+          <t>97,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,87%</t>
         </is>
       </c>
     </row>
@@ -10122,12 +10122,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>61511</t>
+          <t>60098</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>96961</t>
+          <t>94125</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10137,12 +10137,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>3,64%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10157,12 +10157,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>59852</t>
+          <t>61045</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>96283</t>
+          <t>97964</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10172,12 +10172,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>3,36%</t>
+          <t>3,42%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10192,12 +10192,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>130383</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>179356</t>
+          <t>180676</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10207,12 +10207,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,27%</t>
         </is>
       </c>
     </row>
@@ -10235,12 +10235,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>2567372</t>
+          <t>2570208</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>2602822</t>
+          <t>2604235</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10250,12 +10250,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>96,36%</t>
+          <t>96,47%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>97,69%</t>
+          <t>97,74%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10270,12 +10270,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2771032</t>
+          <t>2769351</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>2807463</t>
+          <t>2806270</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10285,12 +10285,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>96,64%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>97,91%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10305,12 +10305,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5352292</t>
+          <t>5350972</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>5401606</t>
+          <t>5401265</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10320,12 +10320,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>96,76%</t>
+          <t>96,73%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,64%</t>
         </is>
       </c>
     </row>
